--- a/world_cup_bella_m.xlsx
+++ b/world_cup_bella_m.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Fixed Income\Sales\Andrew Lilley\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7BA56E-5126-4B6E-B408-3699A7F3B45D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30003E23-C353-41CD-9FBD-48D7F84A36BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21450" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21450" windowHeight="12450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scoring Rules" sheetId="1" r:id="rId1"/>
@@ -315,13 +315,13 @@
     <t>TOTAL ERRORS</t>
   </si>
   <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
     <t>Neymar</t>
+  </si>
+  <si>
+    <t>Home Goals</t>
+  </si>
+  <si>
+    <t>Away Goals</t>
   </si>
 </sst>
 </file>
@@ -2036,10 +2036,10 @@
         <v>29</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>30</v>
@@ -5846,7 +5846,7 @@
         <v>82</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8201,18 +8201,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8411,6 +8411,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0E4EE51-F577-4F8D-9DA9-698AA764DF45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7CC0AC2-8F2A-4E5D-A524-AEB9C9DE977F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -8423,14 +8431,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="745a8124-5753-4a09-8d46-4c5cc3dcc3c9"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0E4EE51-F577-4F8D-9DA9-698AA764DF45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
